--- a/taskbench/data_multimedia/replan_reformat_by_self/data_multimedia_gemini-3.1-flash-lite_intent_audited_replan_edge_repair_ablation_table.xlsx
+++ b/taskbench/data_multimedia/replan_reformat_by_self/data_multimedia_gemini-3.1-flash-lite_intent_audited_replan_edge_repair_ablation_table.xlsx
@@ -186,17 +186,17 @@
       </c>
       <c r="G2" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">87.0718</t>
+          <t xml:space="preserve">87.2351</t>
         </is>
       </c>
       <c r="H2" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">59.4947</t>
+          <t xml:space="preserve">59.8796</t>
         </is>
       </c>
       <c r="I2" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14.439</t>
+          <t xml:space="preserve">14.2497</t>
         </is>
       </c>
       <c r="J2" t="inlineStr" s="2">
@@ -263,47 +263,47 @@
       </c>
       <c r="G3" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">87.7571</t>
+          <t xml:space="preserve">88.2619</t>
         </is>
       </c>
       <c r="H3" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">60.1399</t>
+          <t xml:space="preserve">61.2777</t>
         </is>
       </c>
       <c r="I3" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14.0196</t>
+          <t xml:space="preserve">13.6103</t>
         </is>
       </c>
       <c r="J3" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">0.6853</t>
+          <t xml:space="preserve">1.0268</t>
         </is>
       </c>
       <c r="K3" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">0.6452</t>
+          <t xml:space="preserve">1.3981</t>
         </is>
       </c>
       <c r="L3" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">-0.4194</t>
+          <t xml:space="preserve">-0.6394</t>
         </is>
       </c>
       <c r="M3" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">0.6853</t>
+          <t xml:space="preserve">1.0268</t>
         </is>
       </c>
       <c r="N3" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">0.6452</t>
+          <t xml:space="preserve">1.3981</t>
         </is>
       </c>
       <c r="O3" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">-0.4194</t>
+          <t xml:space="preserve">-0.6394</t>
         </is>
       </c>
     </row>
@@ -340,17 +340,17 @@
       </c>
       <c r="G4" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">87.7571</t>
+          <t xml:space="preserve">88.2619</t>
         </is>
       </c>
       <c r="H4" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">60.293</t>
+          <t xml:space="preserve">61.4707</t>
         </is>
       </c>
       <c r="I4" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14.0196</t>
+          <t xml:space="preserve">13.6103</t>
         </is>
       </c>
       <c r="J4" t="inlineStr" s="2">
@@ -360,7 +360,7 @@
       </c>
       <c r="K4" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">0.1531</t>
+          <t xml:space="preserve">0.193</t>
         </is>
       </c>
       <c r="L4" t="inlineStr" s="2">
@@ -370,17 +370,17 @@
       </c>
       <c r="M4" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">0.6853</t>
+          <t xml:space="preserve">1.0268</t>
         </is>
       </c>
       <c r="N4" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">0.7983</t>
+          <t xml:space="preserve">1.5911</t>
         </is>
       </c>
       <c r="O4" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">-0.4194</t>
+          <t xml:space="preserve">-0.6394</t>
         </is>
       </c>
     </row>
